--- a/01_Input/00_CO Validation/Trinidad & Tobago - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Trinidad & Tobago - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="211" documentId="11_17A891D81675D87D65C4FD40FDCD662C781F2CF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E4C8170-B1DA-479C-96E8-E07FF5D5C6A4}"/>
+  <xr:revisionPtr revIDLastSave="222" documentId="11_17A891D81675D87D65C4FD40FDCD662C781F2CF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{932A4149-B890-4575-B245-5503C85AEDCB}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14,6 +14,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="106">
   <si>
     <t>Project ID</t>
   </si>
@@ -169,7 +172,7 @@
     <t xml:space="preserve">This indicator is on-track.  An analysis of existing tax systems was completed, and a draft fiscal incentive report was completed to promote energy-efficient technologies for the refrigeration and air-conditioning sectors. Stakeholder consultations are in process. </t>
   </si>
   <si>
-    <t>Other Energy Services</t>
+    <t>Energy Saved (MJ)</t>
   </si>
   <si>
     <t>(GEF Core Indicator 6.3):
@@ -209,9 +212,6 @@
     <t>108 kW of solar PV was added from a total of 12 installations</t>
   </si>
   <si>
-    <t>to the CO: Please estimate the number of MW.</t>
-  </si>
-  <si>
     <t>Close the gap on energy access</t>
   </si>
   <si>
@@ -243,9 +243,6 @@
   </si>
   <si>
     <t>Improving community climate resilience in Matelot by implementing green solutions to address its electricity, water and food limitations.</t>
-  </si>
-  <si>
-    <t>26,000USD</t>
   </si>
   <si>
     <t>No. of activities supported by installation</t>
@@ -259,6 +256,9 @@
 Women: 100 (40%)</t>
   </si>
   <si>
+    <t>Other Energy Services</t>
+  </si>
+  <si>
     <t>(GEF Core Indicator 6.2):
 Number of GHG emissions avoided over the investment period of the project (direct).</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>80-180</t>
+  </si>
+  <si>
+    <t>26,000USD</t>
   </si>
   <si>
     <t>Tier</t>
@@ -630,7 +633,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -701,9 +704,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -711,51 +711,198 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -770,156 +917,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1244,78 +1241,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30.75">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="89" t="s">
+      <c r="C1" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="89" t="s">
+      <c r="D1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="85" t="s">
+      <c r="L1" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="51" t="s">
+      <c r="M1" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="51" t="s">
+      <c r="N1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="51" t="s">
+      <c r="O1" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="51" t="s">
+      <c r="P1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="51" t="s">
+      <c r="Q1" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="51" t="s">
+      <c r="R1" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="51" t="s">
+      <c r="S1" s="30" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="204.75" customHeight="1">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="96" t="s">
+      <c r="C2" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="83">
+      <c r="D2" s="58">
         <v>5152392</v>
       </c>
-      <c r="E2" s="87" t="s">
+      <c r="E2" s="62" t="s">
         <v>22</v>
       </c>
       <c r="F2" s="19" t="s">
@@ -1330,31 +1327,31 @@
       <c r="I2" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="52"/>
-      <c r="K2" s="84">
+      <c r="J2" s="31"/>
+      <c r="K2" s="59">
         <v>0.4</v>
       </c>
-      <c r="L2" s="82" t="s">
+      <c r="L2" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="74"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52" t="s">
+      <c r="M2" s="49"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="52" t="s">
+      <c r="P2" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
     </row>
     <row r="3" spans="1:19" ht="108" customHeight="1">
-      <c r="A3" s="92"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="87" t="s">
+      <c r="A3" s="67"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="62" t="s">
         <v>29</v>
       </c>
       <c r="F3" s="19" t="s">
@@ -1369,27 +1366,27 @@
       <c r="I3" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="52"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52" t="s">
+      <c r="J3" s="31"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="52" t="s">
+      <c r="P3" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="52"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
     </row>
     <row r="4" spans="1:19" ht="76.5">
-      <c r="A4" s="92"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="87" t="s">
+      <c r="A4" s="67"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="62" t="s">
         <v>32</v>
       </c>
       <c r="F4" s="19" t="s">
@@ -1404,31 +1401,31 @@
       <c r="I4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="52"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52" t="s">
+      <c r="J4" s="31"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="52" t="s">
+      <c r="P4" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52" t="s">
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="S4" s="52" t="s">
+      <c r="S4" s="31" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="158.25" customHeight="1">
-      <c r="A5" s="92"/>
-      <c r="B5" s="92"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="87" t="s">
+      <c r="A5" s="67"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="62" t="s">
         <v>32</v>
       </c>
       <c r="F5" s="19" t="s">
@@ -1443,150 +1440,150 @@
       <c r="I5" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="52"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52" t="s">
+      <c r="J5" s="31"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P5" s="52" t="s">
+      <c r="P5" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="52" t="s">
+      <c r="Q5" s="31"/>
+      <c r="R5" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="S5" s="52" t="s">
+      <c r="S5" s="31" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="144" customHeight="1">
-      <c r="A6" s="92"/>
-      <c r="B6" s="92"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="87" t="s">
+      <c r="A6" s="67"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="79" t="s">
+      <c r="F6" s="54" t="s">
         <v>39</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="79">
+      <c r="H6" s="54">
         <v>651000</v>
       </c>
       <c r="I6" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="52"/>
-      <c r="K6" s="72"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52" t="s">
+      <c r="J6" s="31"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P6" s="52" t="s">
+      <c r="P6" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="52"/>
-      <c r="R6" s="52"/>
-      <c r="S6" s="52"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
     </row>
     <row r="7" spans="1:19" ht="78.75" customHeight="1">
-      <c r="A7" s="92"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="87" t="s">
+      <c r="A7" s="67"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="79" t="s">
+      <c r="F7" s="54" t="s">
         <v>41</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="79">
+      <c r="H7" s="54">
         <v>2</v>
       </c>
       <c r="I7" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="52"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="86"/>
-      <c r="M7" s="74"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52" t="s">
+      <c r="J7" s="31"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P7" s="52" t="s">
+      <c r="P7" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="52" t="s">
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="S7" s="52" t="s">
+      <c r="S7" s="31" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="25" customFormat="1" ht="155.25" customHeight="1">
-      <c r="A8" s="93"/>
-      <c r="B8" s="93"/>
-      <c r="C8" s="98"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="88" t="s">
+      <c r="A8" s="68"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="80" t="s">
+      <c r="F8" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="27">
         <v>0</v>
       </c>
-      <c r="H8" s="28">
-        <v>22</v>
-      </c>
-      <c r="I8" s="81" t="s">
+      <c r="H8" s="27">
+        <v>3600000</v>
+      </c>
+      <c r="I8" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="53"/>
-      <c r="K8" s="99"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="75" t="s">
+      <c r="J8" s="32"/>
+      <c r="K8" s="74"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="N8" s="53"/>
-      <c r="O8" s="52" t="s">
+      <c r="N8" s="32"/>
+      <c r="O8" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P8" s="52" t="s">
+      <c r="P8" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="Q8" s="52"/>
-      <c r="R8" s="52"/>
-      <c r="S8" s="52"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
     </row>
     <row r="9" spans="1:19" ht="91.5" customHeight="1">
-      <c r="A9" s="65">
+      <c r="A9" s="41">
         <v>110728</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="69">
+      <c r="D9" s="45">
         <v>2665440</v>
       </c>
-      <c r="E9" s="59" t="s">
+      <c r="E9" s="36" t="s">
         <v>49</v>
       </c>
       <c r="F9" s="6" t="s">
@@ -1601,70 +1598,68 @@
       <c r="I9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="52"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="77" t="s">
+      <c r="J9" s="31"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="M9" s="74"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="52" t="s">
+      <c r="M9" s="49"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P9" s="52" t="s">
+      <c r="P9" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="Q9" s="52"/>
-      <c r="R9" s="52"/>
-      <c r="S9" s="52"/>
-    </row>
-    <row r="10" spans="1:19" s="27" customFormat="1" ht="60.75">
-      <c r="A10" s="65"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="60" t="s">
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+    </row>
+    <row r="10" spans="1:19" s="26" customFormat="1" ht="60.75">
+      <c r="A10" s="41"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="9">
         <v>0</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="9">
         <v>0.108</v>
       </c>
-      <c r="I10" s="26" t="s">
+      <c r="I10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="55"/>
-      <c r="K10" s="73"/>
-      <c r="L10" s="77"/>
-      <c r="M10" s="75" t="s">
+      <c r="J10" s="31"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="75"/>
+      <c r="N10" s="76"/>
+      <c r="O10" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="N10" s="56"/>
-      <c r="O10" s="52" t="s">
+      <c r="P10" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="P10" s="52" t="s">
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+    </row>
+    <row r="11" spans="1:19" ht="76.5">
+      <c r="A11" s="42"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="Q10" s="52"/>
-      <c r="R10" s="52"/>
-      <c r="S10" s="52"/>
-    </row>
-    <row r="11" spans="1:19" ht="76.5">
-      <c r="A11" s="66"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="G11" s="9">
         <v>0</v>
@@ -1673,33 +1668,33 @@
         <v>36</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="J11" s="52"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="78"/>
-      <c r="M11" s="74"/>
-      <c r="N11" s="52"/>
-      <c r="O11" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="31"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="49"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P11" s="52" t="s">
+      <c r="P11" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="Q11" s="52"/>
-      <c r="R11" s="52"/>
-      <c r="S11" s="52"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
     </row>
     <row r="12" spans="1:19" ht="76.5" hidden="1" customHeight="1">
-      <c r="A12" s="61"/>
-      <c r="B12" s="62"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="64"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="40"/>
       <c r="E12" s="6" t="s">
         <v>32</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G12" s="9">
         <v>0</v>
@@ -1708,33 +1703,33 @@
         <v>5</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="76"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="52"/>
-      <c r="O12" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P12" s="52" t="s">
+      <c r="P12" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="Q12" s="52"/>
-      <c r="R12" s="52"/>
-      <c r="S12" s="52"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
     </row>
     <row r="13" spans="1:19" ht="76.5" hidden="1" customHeight="1">
       <c r="A13" s="9"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="58"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="G13" s="9">
         <v>0</v>
@@ -1743,39 +1738,37 @@
         <v>100000</v>
       </c>
       <c r="I13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+    </row>
+    <row r="14" spans="1:19" s="26" customFormat="1" ht="106.5">
+      <c r="A14" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="52"/>
-      <c r="O13" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="P13" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q13" s="52"/>
-      <c r="R13" s="52"/>
-      <c r="S13" s="52"/>
-    </row>
-    <row r="14" spans="1:19" s="27" customFormat="1" ht="106.5">
-      <c r="A14" s="24" t="s">
+      <c r="B14" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="C14" s="27"/>
+      <c r="D14" s="77">
+        <v>26000</v>
+      </c>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27" t="s">
         <v>67</v>
-      </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>69</v>
       </c>
       <c r="G14" s="24">
         <v>0</v>
@@ -1783,25 +1776,25 @@
       <c r="H14" s="24">
         <v>2</v>
       </c>
-      <c r="I14" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="54" t="s">
+      <c r="I14" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="N14" s="55"/>
-      <c r="O14" s="52" t="s">
+      <c r="N14" s="34"/>
+      <c r="O14" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P14" s="52" t="s">
+      <c r="P14" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="Q14" s="52"/>
-      <c r="R14" s="52"/>
-      <c r="S14" s="52"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
     </row>
     <row r="21" spans="3:3">
       <c r="C21" s="8"/>
@@ -1896,16 +1889,16 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="321">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="34">
+      <c r="D2" s="84">
         <v>5152392</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -1918,17 +1911,17 @@
         <v>24</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="152.25">
-      <c r="A3" s="31"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="84"/>
       <c r="E3" s="5" t="s">
         <v>29</v>
       </c>
@@ -1946,10 +1939,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="91.5">
-      <c r="A4" s="31"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="34"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="84"/>
       <c r="E4" s="5" t="s">
         <v>32</v>
       </c>
@@ -1967,10 +1960,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="259.5">
-      <c r="A5" s="31"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="34"/>
+      <c r="A5" s="78"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="84"/>
       <c r="E5" s="5" t="s">
         <v>32</v>
       </c>
@@ -1988,31 +1981,31 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="244.5">
-      <c r="A6" s="31"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="34"/>
+      <c r="A6" s="78"/>
+      <c r="B6" s="80"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="84"/>
       <c r="E6" s="5" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G6" s="10">
         <v>0</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="137.25">
-      <c r="A7" s="31"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="34"/>
+      <c r="A7" s="78"/>
+      <c r="B7" s="80"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="84"/>
       <c r="E7" s="6" t="s">
         <v>32</v>
       </c>
@@ -2030,12 +2023,12 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="259.5">
-      <c r="A8" s="30"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="41"/>
+      <c r="A8" s="79"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="85"/>
       <c r="E8" s="13" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>44</v>
@@ -2051,16 +2044,16 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="91.5" customHeight="1">
-      <c r="A9" s="35">
+      <c r="A9" s="86">
         <v>110728</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="92">
         <v>2665440</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -2073,17 +2066,17 @@
         <v>0</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="60.75">
-      <c r="A10" s="35"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="38"/>
+      <c r="A10" s="86"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="92"/>
       <c r="E10" s="5" t="s">
         <v>53</v>
       </c>
@@ -2094,22 +2087,22 @@
         <v>0</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="76.5">
-      <c r="A11" s="35"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="38"/>
+      <c r="A11" s="86"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="92"/>
       <c r="E11" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11" s="9">
         <v>0</v>
@@ -2118,19 +2111,19 @@
         <v>36</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="76.5">
-      <c r="A12" s="35"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="38"/>
+      <c r="A12" s="86"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="92"/>
       <c r="E12" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G12" s="9">
         <v>0</v>
@@ -2139,19 +2132,19 @@
         <v>5</v>
       </c>
       <c r="I12" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="76.5">
+      <c r="A13" s="87"/>
+      <c r="B13" s="89"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="13" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="76.5">
-      <c r="A13" s="42"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="13" t="s">
+      <c r="F13" s="18" t="s">
         <v>63</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>64</v>
       </c>
       <c r="G13" s="16">
         <v>0</v>
@@ -2160,25 +2153,25 @@
         <v>100000</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="106.5">
       <c r="A14" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>66</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>67</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E14" s="20" t="s">
         <v>49</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G14" s="10">
         <v>0</v>
@@ -2187,7 +2180,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J14" s="22"/>
     </row>
@@ -2251,7 +2244,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="94" t="s">
         <v>78</v>
       </c>
       <c r="B2" t="s">
@@ -2262,7 +2255,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="46"/>
+      <c r="A3" s="94"/>
       <c r="B3" t="s">
         <v>53</v>
       </c>
@@ -2271,7 +2264,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="46"/>
+      <c r="A4" s="94"/>
       <c r="B4" t="s">
         <v>81</v>
       </c>
@@ -2280,7 +2273,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="95" t="s">
         <v>83</v>
       </c>
       <c r="B5" t="s">
@@ -2291,7 +2284,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="47"/>
+      <c r="A6" s="95"/>
       <c r="B6" t="s">
         <v>86</v>
       </c>
@@ -2300,7 +2293,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="47"/>
+      <c r="A7" s="95"/>
       <c r="B7" t="s">
         <v>88</v>
       </c>
@@ -2309,7 +2302,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="47"/>
+      <c r="A8" s="95"/>
       <c r="B8" t="s">
         <v>90</v>
       </c>
@@ -2318,16 +2311,16 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="47"/>
+      <c r="A9" s="95"/>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="96" t="s">
         <v>93</v>
       </c>
       <c r="B10" t="s">
@@ -2338,7 +2331,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="48"/>
+      <c r="A11" s="96"/>
       <c r="B11" t="s">
         <v>96</v>
       </c>
@@ -2347,7 +2340,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="97" t="s">
         <v>98</v>
       </c>
       <c r="B12" t="s">
@@ -2358,7 +2351,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="49"/>
+      <c r="A13" s="97"/>
       <c r="B13" t="s">
         <v>29</v>
       </c>
@@ -2367,9 +2360,9 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="49"/>
+      <c r="A14" s="97"/>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
         <v>101</v>
@@ -2420,15 +2413,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -2677,14 +2661,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A004395-6E39-4F77-B900-4574E2DB0C85}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7AC1A98-C21D-4D7B-9D3E-59462D5655A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{777AFA6C-3D83-4A0B-B595-9ACE5A90247F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{777AFA6C-3D83-4A0B-B595-9ACE5A90247F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7AC1A98-C21D-4D7B-9D3E-59462D5655A1}"/>
 </file>
--- a/01_Input/00_CO Validation/Trinidad & Tobago - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Trinidad & Tobago - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="275" documentId="11_17A891D81675D87D65C4FD40FDCD662C781F2CF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B070E12-30FB-475B-B3CD-8B84907C6F1E}"/>
+  <xr:revisionPtr revIDLastSave="277" documentId="11_17A891D81675D87D65C4FD40FDCD662C781F2CF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62870971-DC9A-4C94-9C43-B2D36869E8BD}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="118">
   <si>
     <t>Project ID</t>
   </si>
@@ -98,7 +98,7 @@
     <t>Policy Population</t>
   </si>
   <si>
-    <t>5957/ 117647</t>
+    <t>5957, 117647</t>
   </si>
   <si>
     <t>Energy Efficiency through the Development of Low-carbon RAC Technologies in Trinidad and Tobago</t>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t xml:space="preserve">This projects aims to install a solar system at the Matelot Police Youth Club to address the electricity shortages in the area. The system will support the club's computer lab and hydroponics systems. </t>
+  </si>
+  <si>
+    <t>5957/ 117647</t>
   </si>
   <si>
     <t>Capacity Training</t>
@@ -869,6 +872,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -916,9 +922,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1334,7 +1337,7 @@
       <c r="D2" s="54">
         <v>5152392</v>
       </c>
-      <c r="E2" s="98" t="s">
+      <c r="E2" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="16" t="s">
@@ -1388,7 +1391,7 @@
       <c r="B3" s="61"/>
       <c r="C3" s="66"/>
       <c r="D3" s="63"/>
-      <c r="E3" s="98" t="s">
+      <c r="E3" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F3" s="16" t="s">
@@ -1438,7 +1441,7 @@
       <c r="B4" s="61"/>
       <c r="C4" s="66"/>
       <c r="D4" s="63"/>
-      <c r="E4" s="98" t="s">
+      <c r="E4" s="82" t="s">
         <v>19</v>
       </c>
       <c r="F4" s="16" t="s">
@@ -1502,7 +1505,7 @@
       <c r="B5" s="61"/>
       <c r="C5" s="66"/>
       <c r="D5" s="63"/>
-      <c r="E5" s="98" t="s">
+      <c r="E5" s="82" t="s">
         <v>19</v>
       </c>
       <c r="F5" s="16" t="s">
@@ -1616,7 +1619,7 @@
       <c r="B7" s="61"/>
       <c r="C7" s="66"/>
       <c r="D7" s="63"/>
-      <c r="E7" s="98" t="s">
+      <c r="E7" s="82" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="50" t="s">
@@ -1680,7 +1683,7 @@
       <c r="B8" s="62"/>
       <c r="C8" s="67"/>
       <c r="D8" s="64"/>
-      <c r="E8" s="98" t="s">
+      <c r="E8" s="82" t="s">
         <v>50</v>
       </c>
       <c r="F8" s="51" t="s">
@@ -1729,7 +1732,7 @@
     </row>
     <row r="9" spans="1:32" ht="91.5" customHeight="1">
       <c r="A9" s="37">
-        <v>110728</v>
+        <v>112038</v>
       </c>
       <c r="B9" s="39" t="s">
         <v>54</v>
@@ -1740,7 +1743,7 @@
       <c r="D9" s="41">
         <v>2665440</v>
       </c>
-      <c r="E9" s="98" t="s">
+      <c r="E9" s="82" t="s">
         <v>56</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -1792,7 +1795,7 @@
       <c r="B10" s="39"/>
       <c r="C10" s="42"/>
       <c r="D10" s="41"/>
-      <c r="E10" s="98" t="s">
+      <c r="E10" s="82" t="s">
         <v>59</v>
       </c>
       <c r="F10" s="3" t="s">
@@ -1842,7 +1845,7 @@
       <c r="B11" s="40"/>
       <c r="C11" s="43"/>
       <c r="D11" s="36"/>
-      <c r="E11" s="98" t="s">
+      <c r="E11" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="3" t="s">
@@ -1892,7 +1895,7 @@
       <c r="B12" s="34"/>
       <c r="C12" s="35"/>
       <c r="D12" s="36"/>
-      <c r="E12" s="98"/>
+      <c r="E12" s="82"/>
       <c r="F12" s="3" t="s">
         <v>65</v>
       </c>
@@ -1940,7 +1943,7 @@
       <c r="B13" s="3"/>
       <c r="C13" s="25"/>
       <c r="D13" s="32"/>
-      <c r="E13" s="98"/>
+      <c r="E13" s="82"/>
       <c r="F13" s="3" t="s">
         <v>67</v>
       </c>
@@ -1994,7 +1997,7 @@
       <c r="D14" s="71">
         <v>26000</v>
       </c>
-      <c r="E14" s="98"/>
+      <c r="E14" s="82"/>
       <c r="F14" s="24" t="s">
         <v>71</v>
       </c>
@@ -2165,20 +2168,20 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="321">
-      <c r="A2" s="82" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="84" t="s">
+      <c r="A2" s="83" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="88">
+      <c r="D2" s="89">
         <v>5152392</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>25</v>
@@ -2187,19 +2190,19 @@
         <v>26</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="152.25">
-      <c r="A3" s="82"/>
-      <c r="B3" s="84"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="88"/>
+      <c r="A3" s="83"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="89"/>
       <c r="E3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>32</v>
@@ -2215,10 +2218,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="91.5">
-      <c r="A4" s="82"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="88"/>
+      <c r="A4" s="83"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="89"/>
       <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
@@ -2236,10 +2239,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="259.5">
-      <c r="A5" s="82"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="88"/>
+      <c r="A5" s="83"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="89"/>
       <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
@@ -2257,31 +2260,31 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="244.5">
-      <c r="A6" s="82"/>
-      <c r="B6" s="84"/>
-      <c r="C6" s="86"/>
-      <c r="D6" s="88"/>
+      <c r="A6" s="83"/>
+      <c r="B6" s="85"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="89"/>
       <c r="E6" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" s="7">
         <v>0</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="137.25">
-      <c r="A7" s="82"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="88"/>
+      <c r="A7" s="83"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="89"/>
       <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
@@ -2299,12 +2302,12 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="259.5">
-      <c r="A8" s="83"/>
-      <c r="B8" s="85"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="89"/>
+      <c r="A8" s="84"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="90"/>
       <c r="E8" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>51</v>
@@ -2320,16 +2323,16 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="91.5" customHeight="1">
-      <c r="A9" s="90">
+      <c r="A9" s="91">
         <v>110728</v>
       </c>
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="94" t="s">
+      <c r="C9" s="95" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="96">
+      <c r="D9" s="97">
         <v>2665440</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -2342,17 +2345,17 @@
         <v>0</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="60.75">
-      <c r="A10" s="90"/>
-      <c r="B10" s="92"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="96"/>
+      <c r="A10" s="91"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="97"/>
       <c r="E10" s="2" t="s">
         <v>59</v>
       </c>
@@ -2363,19 +2366,19 @@
         <v>0</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="76.5">
-      <c r="A11" s="90"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="96"/>
+      <c r="A11" s="91"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="97"/>
       <c r="E11" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>63</v>
@@ -2391,10 +2394,10 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="76.5">
-      <c r="A12" s="90"/>
-      <c r="B12" s="92"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="96"/>
+      <c r="A12" s="91"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="97"/>
       <c r="E12" s="2" t="s">
         <v>19</v>
       </c>
@@ -2412,12 +2415,12 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="76.5">
-      <c r="A13" s="91"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="97"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="98"/>
       <c r="E13" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>67</v>
@@ -2441,7 +2444,7 @@
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>56</v>
@@ -2521,7 +2524,7 @@
         <v>56</v>
       </c>
       <c r="B2" s="74" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2529,63 +2532,63 @@
         <v>59</v>
       </c>
       <c r="B3" s="74" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
       <c r="A4" s="99" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B4" s="74" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
       <c r="A5" s="99" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="91.5">
       <c r="A6" s="99" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B6" s="74" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45.75">
       <c r="A7" s="99" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" s="74" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45.75">
       <c r="A8" s="99" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B8" s="74" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45.75">
       <c r="A9" s="99" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B9" s="74" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
       <c r="A10" s="99" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B10" s="100" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30.75">
@@ -2593,47 +2596,47 @@
         <v>50</v>
       </c>
       <c r="B11" s="100" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45.75">
       <c r="A12" s="99" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="74" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30.75">
       <c r="A13" s="99" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B13" s="100" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="99" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B14" s="100" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30.75">
       <c r="A15" s="99" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B15" s="100" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30.75">
       <c r="A16" s="99" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B16" s="100" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
@@ -2641,31 +2644,31 @@
         <v>24</v>
       </c>
       <c r="B17" s="74" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
       <c r="A18" s="99" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="100" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
       <c r="A19" s="99" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B19" s="100" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
       <c r="A20" s="99" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="100" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
@@ -2673,15 +2676,15 @@
         <v>19</v>
       </c>
       <c r="B21" s="101" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
       <c r="A22" s="99" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B22" s="100" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2699,8 +2702,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2725,6 +2739,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2804,6 +2819,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2947,25 +2967,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7AC1A98-C21D-4D7B-9D3E-59462D5655A1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{777AFA6C-3D83-4A0B-B595-9ACE5A90247F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A004395-6E39-4F77-B900-4574E2DB0C85}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A004395-6E39-4F77-B900-4574E2DB0C85}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9DC77E2-72A3-4783-AE1C-D17056907EA9}"/>
 </file>
--- a/01_Input/00_CO Validation/Trinidad & Tobago - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Trinidad & Tobago - Energy Projects.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="277" documentId="11_17A891D81675D87D65C4FD40FDCD662C781F2CF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62870971-DC9A-4C94-9C43-B2D36869E8BD}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="314" documentId="11_17A891D81675D87D65C4FD40FDCD662C781F2CF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BC83590-1BFB-443A-B514-6B957CC38231}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId1"/>
-    <sheet name="Projects" sheetId="1" r:id="rId2"/>
-    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId1"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId2"/>
+    <sheet name="Projects (3)" sheetId="4" r:id="rId3"/>
+    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="153">
   <si>
     <t>Project ID</t>
   </si>
@@ -104,7 +110,7 @@
     <t>Energy Efficiency through the Development of Low-carbon RAC Technologies in Trinidad and Tobago</t>
   </si>
   <si>
-    <t>https://open.undp.org/projects/00117647</t>
+    <t>https://open.undp.org/projects/00117647 https://co.pims.undp.org/project/view?id=5957</t>
   </si>
   <si>
     <t>Capacity Building Training</t>
@@ -124,13 +130,13 @@
 Women: 73 (25%)</t>
   </si>
   <si>
-    <t>Non-VF</t>
+    <t>GEF</t>
+  </si>
+  <si>
+    <t>VF</t>
   </si>
   <si>
     <t>Accelerating just energy transition</t>
-  </si>
-  <si>
-    <t>VF</t>
   </si>
   <si>
     <t>Energy Efficiency</t>
@@ -221,6 +227,12 @@
     <t xml:space="preserve">12 sites had solar PV systems installed on their rooftops that would enable electricity from a renewable energy source to be consumed; 700 beneficiaries (direct usage) estimated to date </t>
   </si>
   <si>
+    <t>European Commission</t>
+  </si>
+  <si>
+    <t>Non-VF</t>
+  </si>
+  <si>
     <t>Energy (MW added)</t>
   </si>
   <si>
@@ -264,6 +276,9 @@
   </si>
   <si>
     <t>5957/ 117647</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00117647</t>
   </si>
   <si>
     <t>Capacity Training</t>
@@ -297,6 +312,127 @@
   </si>
   <si>
     <t>26,000USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strengthening technical capacities in the formal academic sector and in the specialized technical CSO (ARIA) to promote market development of energy-efficient, low-carbon refrigeration and cooling systems, including design, assembling, installation, operation, and maintenance. This indicator has been achieved. The number of persons trained and in attendance at awareness sessions were collected and reported on by the Project Management Unit.  This information was de-aggregated by gender and recorded in a project beneficiaries database. The breakdown is as follows:
+Total participants: 584 (100%)
+Men: 381 (65%)
+Women: 203 (35%)
+</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>This indicator has been achieved. The number of trained professionals and technicians stands at 161. The project continues to build capacities for project investment analysis and customized financing mechanisms in the financial sector to support market change for energy efficient RAC systems.</t>
+  </si>
+  <si>
+    <t>Efficiency</t>
+  </si>
+  <si>
+    <t>This indicator has been achieved.  The Trinidad and Tobago Bureau of Standards has developed and published the Refrigeration Code of the Trinidad and Tobago Bureau of Standards. Its title is "Refrigeration and Airconditioning Sector ( TTS-663_2023). The code includes District Cooling Systems (DCS) and Combined Cooling, Heating, and Power Systems (CCHP)</t>
+  </si>
+  <si>
+    <t>This indicator has been achieved. The Trinidad and Tobago Bureau of Standards (TTBS) adopted the Minimum Energy Performance Standards (MEPs) developed regionally by CARICOM Regional Organization for Standards and Quality (CROSQ), and it has been implemented as a voluntary standard. The project will assist TTBS in transitioning the standard to compulsory leveraging the support of the project's Legal Expert and MEPs Specialist.
+The standards implemented are as follows:
+- Standards Energy Labelling - Air Conditioners – Requirements (TTS/CRS 59:2021) and
+- TTS/CRS 57:2021- Energy Labelling - Refrigerating Appliances – Requirements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This indicator has been met. The Environmental Policy and Planning Division (EPPD) of the Ministry of Planning and Development (MPD) continuously monitors this indicator through an established CO2 emissions model, which relies on meticulous tracking of project outcomes and outputs. The total number of GHG emissions avoided to date is 752,656 CO2eq </t>
+  </si>
+  <si>
+    <t>This indicator has been achieved. The report on Fiscal incentives and the market Analysis for the RAC sector have been completed. These and the Procurement Roadmap developed through the project are the financial and market mechanisms for developing low-carbon RAC technologies in Trinidad and Tobago.</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This indicator is on-track. An analysis of data sourced from the Trinidad and Tobago Bureau of Standards (TTBS) annual reports on RAC equipment from 2021 to 2024 was perfomed by the PMU. The data was categorized into two groups: Refrigeration Equipment and Air-conditioners. Over the period from 2021 to 2024, the total energy savings achieved through the adoption of energy-saving measures in RAC equipment amounted to 15.91 GWh. The project will continue to provide support to the Trinidad and Tobago Bureau of Standards (TTBS) to implement a system so as to provide additional data for this indicator and inputs for policymakers. </t>
+  </si>
+  <si>
+    <t>2400
+(1200 women)</t>
+  </si>
+  <si>
+    <t>Twelve (12) sites had solar PV systems installed on their rooftops enbling electricity from a renewable energy source to be consumed. Data collected through site usage forms indicated direct usage beneficiaries estimated to date amounts to 12,786 persons (5,887 men, 6899 women).</t>
+  </si>
+  <si>
+    <t>Just</t>
+  </si>
+  <si>
+    <t>NDC Support</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>Project Description: The project aims at an increased availability and use of energy from renewable sources and at improved efficiency levels in the consumption of energy. To this end, the 
+project will include installation of solar energy systems in public utilities and remote communities with 
+increased capacity to maintain solar power systems; provide technical assistance for the operationalization 
+of the new, Renewable Energy (RE)/Energy Efficiency (EE)–conducive policy, legislative and regulatory 
+framework; and support the design and implementation of a public awareness-raising campaign on Energy 
+Efficiency, Correct Pricing and Renewable Energy</t>
+  </si>
+  <si>
+    <t>108 kW of solar PV was added from a total of 12 installations. It is expected that a futher 37 kW of solar PV will be added in 2025.</t>
+  </si>
+  <si>
+    <t>36
+(12 women)</t>
+  </si>
+  <si>
+    <t>92 persons (43 women) thus far were trained in operation and maintenance of the solar PV systems</t>
+  </si>
+  <si>
+    <t>Number of Capacity Building Activities related to RE and EE</t>
+  </si>
+  <si>
+    <t>Four (4) capacity building sessions were conducted in the following areas: 
+1.  Feed-In Tariff (FIT) Implementation Plan for Trinidad and Tobago
+2. Renewable Energy Power Purchase Agreements
+3. Renewable Energy Financial Modelling 
+4. The Renewable Energy Policy &amp; Implementation Plan for Trinidad and Tobago</t>
+  </si>
+  <si>
+    <t>Government Capacity-Building</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of technical papers to support the operationalization of 
+policies and regulations </t>
+  </si>
+  <si>
+    <t>Five (5) technical reports were produced. These included:
+1. The Development of a Renewable Energy (RE) Feed-In Tariff (FIT) Implementation Plan for Trinidad and Tobago
+2. A Baseline Report for Renewable Energy and Energy Efficiency Implementation Assessments
+3. A Report on Assessment and Recommendations for a Renewable Energy and Energy Efficiency Incentive Programme
+4. A Report on a Public-Private Partnership Model for Funding Renewable Energy and Energy Efficiency Projects 
+5. A Draft Renewable Energy Policy for Trinidad and Tobago and Implementation Plan
+Female beneficiaries: N/A</t>
+  </si>
+  <si>
+    <t>Legal Framework</t>
+  </si>
+  <si>
+    <t>Reach 100,000 people with messages on the benefits of using renewable energy and energy efficiency, with 20,000 people already reached in Trinidad and Tobago.</t>
+  </si>
+  <si>
+    <t>Public awareness campaign reached 166,530 persons were reached with messages related to RE/EE/ Energy Pricing. Number of Female beneficiaries: 101,570.</t>
+  </si>
+  <si>
+    <t>Overall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34 tons per annum </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://sgp.undp.org/spacial-itemid-projects-landing-page/spacial-itemid-project-search-results/spacial-itemid-project-detailpage.html?view=projectdetail&amp;id=32045 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The project was able to implement solar system in the Matelot Police Youth Club, a building which had not had electricity for over six years. The activities included installation of the a 5kwh solar system, 2 solar hydroponics and a rainwater harvester. These installations now all the club house to facilitate workshops that positively engage 15 women and 50 youths of the community (27 girls and 23 boys) e.g. music, carpentry, etc.. The indirect beneficiaries are the entire community of Matelot, which are 200 people who can now access electricy in case of outages, which occur at least 2-3 times a week. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEF SGP </t>
   </si>
   <si>
     <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.) </t>
@@ -408,7 +544,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -481,8 +617,63 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -498,6 +689,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -633,11 +830,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -823,9 +1021,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -875,6 +1070,157 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -933,9 +1279,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="3">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1238,10 +1585,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06E55A78-CC0D-479B-BC59-0746D0D8BAF3}">
   <dimension ref="A1:AF27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" customWidth="1"/>
@@ -1259,7 +1607,7 @@
     <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="30.75">
+    <row r="1" spans="1:32" ht="29.1">
       <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
@@ -1293,34 +1641,34 @@
       <c r="K1" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="75" t="s">
+      <c r="L1" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="76" t="s">
+      <c r="M1" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="75" t="s">
+      <c r="N1" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="75" t="s">
+      <c r="O1" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="76" t="s">
+      <c r="P1" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="76" t="s">
+      <c r="Q1" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="77" t="s">
+      <c r="R1" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="78" t="s">
+      <c r="S1" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="77" t="s">
+      <c r="T1" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="78" t="s">
+      <c r="U1" s="77" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1331,13 +1679,13 @@
       <c r="B2" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="82" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="54">
         <v>5152392</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="E2" s="81" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="16" t="s">
@@ -1352,36 +1700,38 @@
       <c r="I2" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="28"/>
+      <c r="J2" s="28" t="s">
+        <v>28</v>
+      </c>
       <c r="K2" s="55">
         <v>0.4</v>
       </c>
-      <c r="L2" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="72"/>
-      <c r="N2" s="80" t="s">
+      <c r="L2" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="81"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="80"/>
       <c r="X2" s="53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y2" s="45"/>
       <c r="Z2" s="28"/>
       <c r="AA2" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB2" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AC2" s="72"/>
+      <c r="AC2" s="71"/>
       <c r="AD2" s="28"/>
       <c r="AE2" s="28"/>
       <c r="AF2" s="28"/>
@@ -1389,9 +1739,9 @@
     <row r="3" spans="1:32" ht="108" customHeight="1">
       <c r="A3" s="61"/>
       <c r="B3" s="61"/>
-      <c r="C3" s="66"/>
+      <c r="C3" s="65"/>
       <c r="D3" s="63"/>
-      <c r="E3" s="82" t="s">
+      <c r="E3" s="81" t="s">
         <v>24</v>
       </c>
       <c r="F3" s="16" t="s">
@@ -1406,42 +1756,44 @@
       <c r="I3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="28"/>
+      <c r="J3" s="28" t="s">
+        <v>28</v>
+      </c>
       <c r="K3" s="44"/>
-      <c r="L3" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="72"/>
-      <c r="N3" s="80" t="s">
+      <c r="L3" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="72"/>
-      <c r="U3" s="81"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="71"/>
+      <c r="P3" s="71"/>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="80"/>
       <c r="X3" s="56"/>
       <c r="Y3" s="45"/>
       <c r="Z3" s="28"/>
       <c r="AA3" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB3" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AC3" s="72"/>
+      <c r="AC3" s="71"/>
       <c r="AD3" s="28"/>
       <c r="AE3" s="28"/>
       <c r="AF3" s="28"/>
     </row>
-    <row r="4" spans="1:32" ht="60.75">
+    <row r="4" spans="1:32" ht="72.599999999999994">
       <c r="A4" s="61"/>
       <c r="B4" s="61"/>
-      <c r="C4" s="66"/>
+      <c r="C4" s="65"/>
       <c r="D4" s="63"/>
-      <c r="E4" s="82" t="s">
+      <c r="E4" s="81" t="s">
         <v>19</v>
       </c>
       <c r="F4" s="16" t="s">
@@ -1456,40 +1808,42 @@
       <c r="I4" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="28"/>
+      <c r="J4" s="28" t="s">
+        <v>28</v>
+      </c>
       <c r="K4" s="44"/>
-      <c r="L4" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" s="72"/>
-      <c r="N4" s="80" t="s">
+      <c r="L4" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="72" t="s">
+      <c r="M4" s="71"/>
+      <c r="N4" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="72" t="s">
+      <c r="P4" s="71"/>
+      <c r="Q4" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="R4" s="72" t="s">
+      <c r="R4" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="S4" s="81"/>
-      <c r="T4" s="72" t="s">
+      <c r="S4" s="80"/>
+      <c r="T4" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="U4" s="81"/>
+      <c r="U4" s="80"/>
       <c r="X4" s="56"/>
       <c r="Y4" s="45"/>
       <c r="Z4" s="28"/>
       <c r="AA4" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB4" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="72" t="s">
+      <c r="AC4" s="71" t="s">
         <v>38</v>
       </c>
       <c r="AD4" s="28"/>
@@ -1503,9 +1857,9 @@
     <row r="5" spans="1:32" ht="158.25" customHeight="1">
       <c r="A5" s="61"/>
       <c r="B5" s="61"/>
-      <c r="C5" s="66"/>
+      <c r="C5" s="65"/>
       <c r="D5" s="63"/>
-      <c r="E5" s="82" t="s">
+      <c r="E5" s="81" t="s">
         <v>19</v>
       </c>
       <c r="F5" s="16" t="s">
@@ -1520,40 +1874,42 @@
       <c r="I5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="J5" s="28"/>
+      <c r="J5" s="28" t="s">
+        <v>28</v>
+      </c>
       <c r="K5" s="44"/>
-      <c r="L5" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5" s="72"/>
-      <c r="N5" s="80" t="s">
+      <c r="L5" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="72" t="s">
+      <c r="M5" s="71"/>
+      <c r="N5" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="72" t="s">
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="R5" s="72" t="s">
+      <c r="R5" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="S5" s="81"/>
-      <c r="T5" s="72" t="s">
+      <c r="S5" s="80"/>
+      <c r="T5" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="U5" s="81"/>
+      <c r="U5" s="80"/>
       <c r="X5" s="56"/>
       <c r="Y5" s="45"/>
       <c r="Z5" s="28"/>
       <c r="AA5" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB5" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AC5" s="72" t="s">
+      <c r="AC5" s="71" t="s">
         <v>38</v>
       </c>
       <c r="AD5" s="28"/>
@@ -1567,7 +1923,7 @@
     <row r="6" spans="1:32" ht="144" customHeight="1">
       <c r="A6" s="61"/>
       <c r="B6" s="61"/>
-      <c r="C6" s="66"/>
+      <c r="C6" s="65"/>
       <c r="D6" s="63"/>
       <c r="E6" s="57" t="s">
         <v>42</v>
@@ -1584,32 +1940,34 @@
       <c r="I6" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="J6" s="28"/>
+      <c r="J6" s="28" t="s">
+        <v>28</v>
+      </c>
       <c r="K6" s="44"/>
-      <c r="L6" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" s="72"/>
-      <c r="N6" s="80" t="s">
+      <c r="L6" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="81"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="81"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="71"/>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="80"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="80"/>
       <c r="X6" s="56"/>
       <c r="Y6" s="45"/>
       <c r="Z6" s="28"/>
       <c r="AA6" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB6" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AC6" s="72"/>
+      <c r="AC6" s="71"/>
       <c r="AD6" s="28"/>
       <c r="AE6" s="28"/>
       <c r="AF6" s="28"/>
@@ -1617,9 +1975,9 @@
     <row r="7" spans="1:32" ht="78.75" customHeight="1">
       <c r="A7" s="61"/>
       <c r="B7" s="61"/>
-      <c r="C7" s="66"/>
+      <c r="C7" s="65"/>
       <c r="D7" s="63"/>
-      <c r="E7" s="82" t="s">
+      <c r="E7" s="81" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="50" t="s">
@@ -1634,40 +1992,42 @@
       <c r="I7" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="28"/>
+      <c r="J7" s="28" t="s">
+        <v>28</v>
+      </c>
       <c r="K7" s="44"/>
-      <c r="L7" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" s="72"/>
-      <c r="N7" s="80" t="s">
+      <c r="L7" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="72" t="s">
+      <c r="M7" s="71"/>
+      <c r="N7" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="72" t="s">
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="R7" s="72" t="s">
+      <c r="R7" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="S7" s="81"/>
-      <c r="T7" s="72" t="s">
+      <c r="S7" s="80"/>
+      <c r="T7" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="U7" s="81"/>
+      <c r="U7" s="80"/>
       <c r="X7" s="56"/>
       <c r="Y7" s="45"/>
       <c r="Z7" s="28"/>
       <c r="AA7" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB7" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AC7" s="72" t="s">
+      <c r="AC7" s="71" t="s">
         <v>38</v>
       </c>
       <c r="AD7" s="28"/>
@@ -1681,9 +2041,9 @@
     <row r="8" spans="1:32" s="22" customFormat="1" ht="155.25" customHeight="1">
       <c r="A8" s="62"/>
       <c r="B8" s="62"/>
-      <c r="C8" s="67"/>
+      <c r="C8" s="66"/>
       <c r="D8" s="64"/>
-      <c r="E8" s="82" t="s">
+      <c r="E8" s="81" t="s">
         <v>50</v>
       </c>
       <c r="F8" s="51" t="s">
@@ -1698,34 +2058,36 @@
       <c r="I8" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="79" t="s">
+      <c r="J8" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M8" s="72"/>
-      <c r="N8" s="80" t="s">
+      <c r="K8" s="67"/>
+      <c r="L8" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="O8" s="72"/>
-      <c r="P8" s="72"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="81"/>
-      <c r="T8" s="72"/>
-      <c r="U8" s="81"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="71"/>
+      <c r="P8" s="71"/>
+      <c r="Q8" s="71"/>
+      <c r="R8" s="71"/>
+      <c r="S8" s="80"/>
+      <c r="T8" s="71"/>
+      <c r="U8" s="80"/>
       <c r="X8" s="59"/>
       <c r="Y8" s="46" t="s">
         <v>53</v>
       </c>
       <c r="Z8" s="29"/>
       <c r="AA8" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB8" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AC8" s="72"/>
+      <c r="AC8" s="71"/>
       <c r="AD8" s="28"/>
       <c r="AE8" s="28"/>
       <c r="AF8" s="28"/>
@@ -1743,7 +2105,7 @@
       <c r="D9" s="41">
         <v>2665440</v>
       </c>
-      <c r="E9" s="82" t="s">
+      <c r="E9" s="81" t="s">
         <v>56</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -1758,48 +2120,50 @@
       <c r="I9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J9" s="28"/>
+      <c r="J9" s="28" t="s">
+        <v>59</v>
+      </c>
       <c r="K9" s="44"/>
-      <c r="L9" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="M9" s="72"/>
-      <c r="N9" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="O9" s="72"/>
-      <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="81"/>
-      <c r="T9" s="72"/>
-      <c r="U9" s="81"/>
+      <c r="L9" s="78" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="71"/>
+      <c r="N9" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="80"/>
+      <c r="T9" s="71"/>
+      <c r="U9" s="80"/>
       <c r="X9" s="48" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="Y9" s="45"/>
       <c r="Z9" s="28"/>
       <c r="AA9" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB9" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="AC9" s="72"/>
+      <c r="AC9" s="71"/>
       <c r="AD9" s="28"/>
       <c r="AE9" s="28"/>
       <c r="AF9" s="28"/>
     </row>
-    <row r="10" spans="1:32" s="23" customFormat="1" ht="60.75">
+    <row r="10" spans="1:32" s="23" customFormat="1" ht="57.95">
       <c r="A10" s="37"/>
       <c r="B10" s="39"/>
       <c r="C10" s="42"/>
       <c r="D10" s="41"/>
-      <c r="E10" s="82" t="s">
-        <v>59</v>
+      <c r="E10" s="81" t="s">
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G10" s="6">
         <v>0</v>
@@ -1808,48 +2172,50 @@
         <v>0.108</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J10" s="28"/>
+        <v>63</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>59</v>
+      </c>
       <c r="K10" s="44"/>
-      <c r="L10" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="M10" s="72"/>
-      <c r="N10" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="81"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="81"/>
+      <c r="L10" s="78" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="71"/>
+      <c r="N10" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" s="71"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="71"/>
+      <c r="S10" s="80"/>
+      <c r="T10" s="71"/>
+      <c r="U10" s="80"/>
       <c r="X10" s="48"/>
-      <c r="Y10" s="69"/>
-      <c r="Z10" s="70"/>
+      <c r="Y10" s="68"/>
+      <c r="Z10" s="69"/>
       <c r="AA10" s="28" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AB10" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="AC10" s="72"/>
+      <c r="AC10" s="71"/>
       <c r="AD10" s="28"/>
       <c r="AE10" s="28"/>
       <c r="AF10" s="28"/>
     </row>
-    <row r="11" spans="1:32" ht="76.5">
+    <row r="11" spans="1:32" ht="72.599999999999994">
       <c r="A11" s="38"/>
       <c r="B11" s="40"/>
       <c r="C11" s="43"/>
       <c r="D11" s="36"/>
-      <c r="E11" s="82" t="s">
+      <c r="E11" s="81" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G11" s="6">
         <v>0</v>
@@ -1858,34 +2224,36 @@
         <v>36</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" s="28"/>
+        <v>66</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>59</v>
+      </c>
       <c r="K11" s="44"/>
-      <c r="L11" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="M11" s="72"/>
-      <c r="N11" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="O11" s="72"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="81"/>
-      <c r="T11" s="72"/>
-      <c r="U11" s="81"/>
+      <c r="L11" s="78" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="71"/>
+      <c r="N11" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="71"/>
+      <c r="U11" s="80"/>
       <c r="X11" s="49"/>
       <c r="Y11" s="45"/>
       <c r="Z11" s="28"/>
       <c r="AA11" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB11" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AC11" s="72"/>
+      <c r="AC11" s="71"/>
       <c r="AD11" s="28"/>
       <c r="AE11" s="28"/>
       <c r="AF11" s="28"/>
@@ -1895,9 +2263,9 @@
       <c r="B12" s="34"/>
       <c r="C12" s="35"/>
       <c r="D12" s="36"/>
-      <c r="E12" s="82"/>
+      <c r="E12" s="81"/>
       <c r="F12" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G12" s="6">
         <v>0</v>
@@ -1906,34 +2274,34 @@
         <v>5</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J12" s="28"/>
       <c r="K12" s="28"/>
-      <c r="L12" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="M12" s="72"/>
-      <c r="N12" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="72"/>
-      <c r="S12" s="81"/>
-      <c r="T12" s="72"/>
-      <c r="U12" s="81"/>
+      <c r="L12" s="78" t="s">
+        <v>60</v>
+      </c>
+      <c r="M12" s="71"/>
+      <c r="N12" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" s="71"/>
+      <c r="P12" s="71"/>
+      <c r="Q12" s="71"/>
+      <c r="R12" s="71"/>
+      <c r="S12" s="80"/>
+      <c r="T12" s="71"/>
+      <c r="U12" s="80"/>
       <c r="X12" s="47"/>
       <c r="Y12" s="28"/>
       <c r="Z12" s="28"/>
       <c r="AA12" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB12" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AC12" s="72"/>
+      <c r="AC12" s="71"/>
       <c r="AD12" s="28"/>
       <c r="AE12" s="28"/>
       <c r="AF12" s="28"/>
@@ -1943,9 +2311,9 @@
       <c r="B13" s="3"/>
       <c r="C13" s="25"/>
       <c r="D13" s="32"/>
-      <c r="E13" s="82"/>
+      <c r="E13" s="81"/>
       <c r="F13" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G13" s="6">
         <v>0</v>
@@ -1954,52 +2322,52 @@
         <v>100000</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J13" s="28"/>
       <c r="K13" s="28"/>
-      <c r="L13" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="M13" s="72"/>
-      <c r="N13" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="O13" s="72"/>
-      <c r="P13" s="72"/>
-      <c r="Q13" s="72"/>
-      <c r="R13" s="72"/>
-      <c r="S13" s="81"/>
-      <c r="T13" s="72"/>
-      <c r="U13" s="81"/>
+      <c r="L13" s="78" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="71"/>
+      <c r="N13" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" s="71"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="80"/>
+      <c r="T13" s="71"/>
+      <c r="U13" s="80"/>
       <c r="X13" s="28"/>
       <c r="Y13" s="28"/>
       <c r="Z13" s="28"/>
       <c r="AA13" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB13" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AC13" s="72"/>
+      <c r="AC13" s="71"/>
       <c r="AD13" s="28"/>
       <c r="AE13" s="28"/>
       <c r="AF13" s="28"/>
     </row>
-    <row r="14" spans="1:32" s="23" customFormat="1" ht="106.5">
+    <row r="14" spans="1:32" s="23" customFormat="1" ht="99.95">
       <c r="A14" s="21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="71">
+      <c r="D14" s="70">
         <v>26000</v>
       </c>
-      <c r="E14" s="82"/>
+      <c r="E14" s="81"/>
       <c r="F14" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G14" s="21">
         <v>0</v>
@@ -2008,36 +2376,36 @@
         <v>2</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J14" s="31"/>
       <c r="K14" s="31"/>
-      <c r="L14" s="79" t="s">
-        <v>28</v>
-      </c>
-      <c r="M14" s="72"/>
-      <c r="N14" s="80" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" s="72"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="72"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="81"/>
-      <c r="T14" s="72"/>
-      <c r="U14" s="81"/>
+      <c r="L14" s="78" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14" s="71"/>
+      <c r="N14" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O14" s="71"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="71"/>
+      <c r="S14" s="80"/>
+      <c r="T14" s="71"/>
+      <c r="U14" s="80"/>
       <c r="X14" s="31"/>
       <c r="Y14" s="30" t="s">
         <v>53</v>
       </c>
       <c r="Z14" s="31"/>
       <c r="AA14" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB14" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="AC14" s="72"/>
+      <c r="AC14" s="71"/>
       <c r="AD14" s="28"/>
       <c r="AE14" s="28"/>
       <c r="AF14" s="28"/>
@@ -2125,7 +2493,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="20.7109375" customWidth="1"/>
@@ -2167,21 +2535,21 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="321">
-      <c r="A2" s="83" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="85" t="s">
+    <row r="2" spans="1:10" ht="290.10000000000002">
+      <c r="A2" s="133" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="87" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="89">
+      <c r="C2" s="137" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="139">
         <v>5152392</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>25</v>
@@ -2190,19 +2558,19 @@
         <v>26</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="152.25">
-      <c r="A3" s="83"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="89"/>
+    <row r="3" spans="1:10" ht="144.94999999999999">
+      <c r="A3" s="133"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="139"/>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>32</v>
@@ -2217,11 +2585,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="91.5">
-      <c r="A4" s="83"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="89"/>
+    <row r="4" spans="1:10" ht="87">
+      <c r="A4" s="133"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="139"/>
       <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
@@ -2238,11 +2606,11 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="259.5">
-      <c r="A5" s="83"/>
-      <c r="B5" s="85"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="89"/>
+    <row r="5" spans="1:10" ht="246.6">
+      <c r="A5" s="133"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="139"/>
       <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
@@ -2259,32 +2627,32 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="244.5">
-      <c r="A6" s="83"/>
-      <c r="B6" s="85"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="89"/>
+    <row r="6" spans="1:10" ht="217.5">
+      <c r="A6" s="133"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="139"/>
       <c r="E6" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G6" s="7">
         <v>0</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="137.25">
-      <c r="A7" s="83"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="89"/>
+    <row r="7" spans="1:10" ht="116.1">
+      <c r="A7" s="133"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="139"/>
       <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
@@ -2301,13 +2669,13 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="259.5">
-      <c r="A8" s="84"/>
-      <c r="B8" s="86"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="90"/>
+    <row r="8" spans="1:10" ht="246.6">
+      <c r="A8" s="134"/>
+      <c r="B8" s="136"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="140"/>
       <c r="E8" s="10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>51</v>
@@ -2323,16 +2691,16 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="91.5" customHeight="1">
-      <c r="A9" s="91">
+      <c r="A9" s="141">
         <v>110728</v>
       </c>
-      <c r="B9" s="93" t="s">
+      <c r="B9" s="143" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="95" t="s">
+      <c r="C9" s="145" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="97">
+      <c r="D9" s="147">
         <v>2665440</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -2345,43 +2713,43 @@
         <v>0</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="60.75">
-      <c r="A10" s="91"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="97"/>
+    <row r="10" spans="1:10" ht="57.95">
+      <c r="A10" s="141"/>
+      <c r="B10" s="143"/>
+      <c r="C10" s="145"/>
+      <c r="D10" s="147"/>
       <c r="E10" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G10" s="6">
         <v>0</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="76.5">
-      <c r="A11" s="91"/>
-      <c r="B11" s="93"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="97"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="72.599999999999994">
+      <c r="A11" s="141"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="147"/>
       <c r="E11" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G11" s="6">
         <v>0</v>
@@ -2390,19 +2758,19 @@
         <v>36</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="76.5">
-      <c r="A12" s="91"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="97"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="72.599999999999994">
+      <c r="A12" s="141"/>
+      <c r="B12" s="143"/>
+      <c r="C12" s="145"/>
+      <c r="D12" s="147"/>
       <c r="E12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G12" s="6">
         <v>0</v>
@@ -2411,19 +2779,19 @@
         <v>5</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="76.5">
-      <c r="A13" s="92"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="98"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="57.95">
+      <c r="A13" s="142"/>
+      <c r="B13" s="144"/>
+      <c r="C13" s="146"/>
+      <c r="D13" s="148"/>
       <c r="E13" s="10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G13" s="13">
         <v>0</v>
@@ -2432,25 +2800,25 @@
         <v>100000</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="106.5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="101.45">
       <c r="A14" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="18" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>56</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G14" s="7">
         <v>0</v>
@@ -2459,7 +2827,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J14" s="19"/>
     </row>
@@ -2504,187 +2872,1370 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D304FC-24B7-4D13-BB8F-0840C2BE331C}">
+  <dimension ref="A1:AF31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="55.42578125" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" customWidth="1"/>
+    <col min="16" max="17" width="26.140625" customWidth="1"/>
+    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.42578125" customWidth="1"/>
+    <col min="20" max="20" width="19.7109375" customWidth="1"/>
+    <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" ht="30.75">
+      <c r="A1" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="75" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="76" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="77" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="213">
+      <c r="A2" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="54">
+        <v>5152392</v>
+      </c>
+      <c r="E2" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="85" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="85">
+        <v>250</v>
+      </c>
+      <c r="I2" s="86" t="s">
+        <v>87</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="55">
+        <v>0.35</v>
+      </c>
+      <c r="L2" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="N2" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="80"/>
+      <c r="X2" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB2" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC2" s="71"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+    </row>
+    <row r="3" spans="1:32" ht="121.5">
+      <c r="A3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="85" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="85">
+        <v>0</v>
+      </c>
+      <c r="H3" s="85">
+        <v>150</v>
+      </c>
+      <c r="I3" s="86" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="44"/>
+      <c r="L3" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="71" t="s">
+        <v>90</v>
+      </c>
+      <c r="N3" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="71"/>
+      <c r="P3" s="71"/>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="80"/>
+      <c r="X3" s="56"/>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB3" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC3" s="71"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+    </row>
+    <row r="4" spans="1:32" ht="106.5">
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="85" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="85">
+        <v>0</v>
+      </c>
+      <c r="H4" s="85">
+        <v>1</v>
+      </c>
+      <c r="I4" s="86" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="44"/>
+      <c r="L4" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="71" t="s">
+        <v>90</v>
+      </c>
+      <c r="N4" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" s="71" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="71"/>
+      <c r="Q4" s="71" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="71" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" s="80"/>
+      <c r="T4" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="U4" s="80"/>
+      <c r="X4" s="56"/>
+      <c r="Y4" s="45"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB4" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC4" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF4" s="28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="198">
+      <c r="A5" s="61"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="85" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="85">
+        <v>3</v>
+      </c>
+      <c r="H5" s="85">
+        <v>5</v>
+      </c>
+      <c r="I5" s="86" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="44"/>
+      <c r="L5" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="71" t="s">
+        <v>90</v>
+      </c>
+      <c r="N5" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="71" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71" t="s">
+        <v>36</v>
+      </c>
+      <c r="R5" s="71" t="s">
+        <v>31</v>
+      </c>
+      <c r="S5" s="80"/>
+      <c r="T5" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="U5" s="80"/>
+      <c r="X5" s="56"/>
+      <c r="Y5" s="45"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB5" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC5" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF5" s="28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="106.5">
+      <c r="A6" s="61"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="87" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="88" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="85">
+        <v>0</v>
+      </c>
+      <c r="H6" s="88">
+        <v>651000</v>
+      </c>
+      <c r="I6" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="44"/>
+      <c r="L6" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="71" t="s">
+        <v>90</v>
+      </c>
+      <c r="N6" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="71"/>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="80"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="80"/>
+      <c r="X6" s="56"/>
+      <c r="Y6" s="45"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB6" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC6" s="71"/>
+      <c r="AD6" s="28"/>
+      <c r="AE6" s="28"/>
+      <c r="AF6" s="28"/>
+    </row>
+    <row r="7" spans="1:32" ht="91.5">
+      <c r="A7" s="61"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="88" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="85">
+        <v>0</v>
+      </c>
+      <c r="H7" s="88">
+        <v>2</v>
+      </c>
+      <c r="I7" s="86" t="s">
+        <v>94</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="44"/>
+      <c r="L7" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="N7" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="71" t="s">
+        <v>47</v>
+      </c>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71" t="s">
+        <v>48</v>
+      </c>
+      <c r="R7" s="71" t="s">
+        <v>49</v>
+      </c>
+      <c r="S7" s="80"/>
+      <c r="T7" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="U7" s="80"/>
+      <c r="X7" s="56"/>
+      <c r="Y7" s="45"/>
+      <c r="Z7" s="28"/>
+      <c r="AA7" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB7" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC7" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD7" s="28"/>
+      <c r="AE7" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF7" s="28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" s="22" customFormat="1" ht="167.25">
+      <c r="A8" s="62"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="81" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="89" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="52">
+        <v>0</v>
+      </c>
+      <c r="H8" s="52">
+        <v>22</v>
+      </c>
+      <c r="I8" s="90" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" s="67"/>
+      <c r="L8" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="71" t="s">
+        <v>90</v>
+      </c>
+      <c r="N8" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" s="71"/>
+      <c r="P8" s="71"/>
+      <c r="Q8" s="71"/>
+      <c r="R8" s="71"/>
+      <c r="S8" s="80"/>
+      <c r="T8" s="71"/>
+      <c r="U8" s="80"/>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="91" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB8" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC8" s="71"/>
+      <c r="AD8" s="28"/>
+      <c r="AE8" s="28"/>
+      <c r="AF8" s="28"/>
+    </row>
+    <row r="9" spans="1:32" ht="76.5">
+      <c r="A9" s="92">
+        <v>112038</v>
+      </c>
+      <c r="B9" s="93" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="94" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="95">
+        <v>2665440</v>
+      </c>
+      <c r="E9" s="96" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="97" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="98">
+        <v>0</v>
+      </c>
+      <c r="H9" s="98" t="s">
+        <v>97</v>
+      </c>
+      <c r="I9" s="97" t="s">
+        <v>98</v>
+      </c>
+      <c r="J9" s="99" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" s="100">
+        <v>0.54</v>
+      </c>
+      <c r="L9" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="N9" s="103" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" s="102"/>
+      <c r="P9" s="102"/>
+      <c r="Q9" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="R9" s="102"/>
+      <c r="S9" s="104" t="s">
+        <v>101</v>
+      </c>
+      <c r="T9" s="102"/>
+      <c r="U9" s="104"/>
+      <c r="V9" s="105"/>
+      <c r="W9" s="105"/>
+      <c r="X9" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y9" s="107"/>
+      <c r="Z9" s="99"/>
+      <c r="AA9" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB9" s="99" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC9" s="102"/>
+      <c r="AD9" s="99"/>
+      <c r="AE9" s="99"/>
+      <c r="AF9" s="99"/>
+    </row>
+    <row r="10" spans="1:32" s="23" customFormat="1" ht="336">
+      <c r="A10" s="92"/>
+      <c r="B10" s="93" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="94"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="96" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="97" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="98">
+        <v>0</v>
+      </c>
+      <c r="H10" s="98">
+        <v>0.108</v>
+      </c>
+      <c r="I10" s="97" t="s">
+        <v>103</v>
+      </c>
+      <c r="J10" s="99" t="s">
+        <v>59</v>
+      </c>
+      <c r="K10" s="108"/>
+      <c r="L10" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="N10" s="103" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" s="102" t="s">
+        <v>47</v>
+      </c>
+      <c r="P10" s="102"/>
+      <c r="Q10" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="R10" s="102"/>
+      <c r="S10" s="104" t="s">
+        <v>101</v>
+      </c>
+      <c r="T10" s="102"/>
+      <c r="U10" s="104"/>
+      <c r="V10" s="105"/>
+      <c r="W10" s="105"/>
+      <c r="X10" s="106"/>
+      <c r="Y10" s="109"/>
+      <c r="Z10" s="110"/>
+      <c r="AA10" s="99" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB10" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC10" s="102"/>
+      <c r="AD10" s="99"/>
+      <c r="AE10" s="99"/>
+      <c r="AF10" s="99"/>
+    </row>
+    <row r="11" spans="1:32" ht="76.5">
+      <c r="A11" s="111"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="113"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="97" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="98">
+        <v>0</v>
+      </c>
+      <c r="H11" s="98" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="97" t="s">
+        <v>105</v>
+      </c>
+      <c r="J11" s="99" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="108"/>
+      <c r="L11" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="N11" s="103" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" s="102"/>
+      <c r="P11" s="102"/>
+      <c r="Q11" s="102" t="s">
+        <v>39</v>
+      </c>
+      <c r="R11" s="102"/>
+      <c r="S11" s="104"/>
+      <c r="T11" s="102"/>
+      <c r="U11" s="104"/>
+      <c r="V11" s="105"/>
+      <c r="W11" s="105"/>
+      <c r="X11" s="115"/>
+      <c r="Y11" s="107"/>
+      <c r="Z11" s="99"/>
+      <c r="AA11" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB11" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC11" s="102"/>
+      <c r="AD11" s="99"/>
+      <c r="AE11" s="99"/>
+      <c r="AF11" s="99"/>
+    </row>
+    <row r="12" spans="1:32" ht="76.5">
+      <c r="A12" s="116"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="114"/>
+      <c r="E12" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="97" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="98">
+        <v>0</v>
+      </c>
+      <c r="H12" s="98">
+        <v>5</v>
+      </c>
+      <c r="I12" s="97" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" s="99"/>
+      <c r="K12" s="99"/>
+      <c r="L12" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="M12" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="N12" s="103" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" s="102"/>
+      <c r="P12" s="102"/>
+      <c r="Q12" s="102"/>
+      <c r="R12" s="102"/>
+      <c r="S12" s="104"/>
+      <c r="T12" s="102"/>
+      <c r="U12" s="104"/>
+      <c r="V12" s="105"/>
+      <c r="W12" s="105"/>
+      <c r="X12" s="119"/>
+      <c r="Y12" s="99"/>
+      <c r="Z12" s="99"/>
+      <c r="AA12" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB12" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC12" s="102"/>
+      <c r="AD12" s="99"/>
+      <c r="AE12" s="99"/>
+      <c r="AF12" s="99"/>
+    </row>
+    <row r="13" spans="1:32" ht="60.75">
+      <c r="A13" s="98"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="121"/>
+      <c r="E13" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="97" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="98">
+        <v>0</v>
+      </c>
+      <c r="H13" s="98">
+        <v>100000</v>
+      </c>
+      <c r="I13" s="97" t="s">
+        <v>70</v>
+      </c>
+      <c r="J13" s="99"/>
+      <c r="K13" s="99"/>
+      <c r="L13" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="N13" s="103" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" s="102"/>
+      <c r="P13" s="102"/>
+      <c r="Q13" s="102"/>
+      <c r="R13" s="102"/>
+      <c r="S13" s="104"/>
+      <c r="T13" s="102"/>
+      <c r="U13" s="104"/>
+      <c r="V13" s="105"/>
+      <c r="W13" s="105"/>
+      <c r="X13" s="99"/>
+      <c r="Y13" s="99"/>
+      <c r="Z13" s="99"/>
+      <c r="AA13" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB13" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC13" s="102"/>
+      <c r="AD13" s="99"/>
+      <c r="AE13" s="99"/>
+      <c r="AF13" s="99"/>
+    </row>
+    <row r="14" spans="1:32" ht="121.5">
+      <c r="A14" s="98"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="121"/>
+      <c r="E14" s="96" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="97" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="98">
+        <v>0</v>
+      </c>
+      <c r="H14" s="98">
+        <v>4</v>
+      </c>
+      <c r="I14" s="97" t="s">
+        <v>107</v>
+      </c>
+      <c r="J14" s="99"/>
+      <c r="K14" s="99"/>
+      <c r="L14" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="N14" s="103" t="s">
+        <v>30</v>
+      </c>
+      <c r="O14" s="102" t="s">
+        <v>47</v>
+      </c>
+      <c r="P14" s="102"/>
+      <c r="Q14" s="102" t="s">
+        <v>108</v>
+      </c>
+      <c r="R14" s="102"/>
+      <c r="S14" s="104"/>
+      <c r="T14" s="102"/>
+      <c r="U14" s="104"/>
+      <c r="V14" s="105"/>
+      <c r="W14" s="105"/>
+      <c r="X14" s="99"/>
+      <c r="Y14" s="99"/>
+      <c r="Z14" s="99"/>
+      <c r="AA14" s="99"/>
+      <c r="AB14" s="102"/>
+      <c r="AD14" s="99"/>
+      <c r="AE14" s="99"/>
+      <c r="AF14" s="99"/>
+    </row>
+    <row r="15" spans="1:32" ht="198">
+      <c r="A15" s="98"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="96" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="97" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="98">
+        <v>0</v>
+      </c>
+      <c r="H15" s="98">
+        <v>5</v>
+      </c>
+      <c r="I15" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
+      <c r="L15" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="M15" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" s="103" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="102" t="s">
+        <v>47</v>
+      </c>
+      <c r="P15" s="102"/>
+      <c r="Q15" s="102" t="s">
+        <v>111</v>
+      </c>
+      <c r="R15" s="102"/>
+      <c r="S15" s="104"/>
+      <c r="T15" s="102" t="s">
+        <v>37</v>
+      </c>
+      <c r="U15" s="104"/>
+      <c r="V15" s="105"/>
+      <c r="W15" s="105"/>
+      <c r="X15" s="99"/>
+      <c r="Y15" s="99"/>
+      <c r="Z15" s="99"/>
+      <c r="AA15" s="99"/>
+      <c r="AB15" s="99"/>
+      <c r="AC15" s="102"/>
+      <c r="AD15" s="99"/>
+      <c r="AE15" s="99"/>
+      <c r="AF15" s="99"/>
+    </row>
+    <row r="16" spans="1:32" ht="121.5">
+      <c r="A16" s="98"/>
+      <c r="B16" s="97"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="121"/>
+      <c r="E16" s="96" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" s="97" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" s="98">
+        <v>0</v>
+      </c>
+      <c r="H16" s="122">
+        <v>100000</v>
+      </c>
+      <c r="I16" s="97" t="s">
+        <v>113</v>
+      </c>
+      <c r="J16" s="99"/>
+      <c r="K16" s="123">
+        <v>0.61</v>
+      </c>
+      <c r="L16" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="N16" s="103" t="s">
+        <v>30</v>
+      </c>
+      <c r="O16" s="102" t="s">
+        <v>114</v>
+      </c>
+      <c r="P16" s="102"/>
+      <c r="Q16" s="102" t="s">
+        <v>36</v>
+      </c>
+      <c r="R16" s="102" t="s">
+        <v>47</v>
+      </c>
+      <c r="S16" s="104"/>
+      <c r="T16" s="102" t="s">
+        <v>37</v>
+      </c>
+      <c r="U16" s="104"/>
+      <c r="V16" s="105"/>
+      <c r="W16" s="105"/>
+      <c r="X16" s="99"/>
+      <c r="Y16" s="99"/>
+      <c r="Z16" s="99"/>
+      <c r="AA16" s="99"/>
+      <c r="AB16" s="99"/>
+      <c r="AC16" s="102"/>
+      <c r="AD16" s="99"/>
+      <c r="AE16" s="99"/>
+      <c r="AF16" s="99"/>
+    </row>
+    <row r="17" spans="1:32" ht="30.75">
+      <c r="A17" s="98"/>
+      <c r="B17" s="97"/>
+      <c r="C17" s="120"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="124" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="125"/>
+      <c r="G17" s="98">
+        <v>0</v>
+      </c>
+      <c r="H17" s="125"/>
+      <c r="I17" s="97" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17" s="99"/>
+      <c r="K17" s="99"/>
+      <c r="L17" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="M17" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="N17" s="103"/>
+      <c r="O17" s="102"/>
+      <c r="P17" s="102"/>
+      <c r="Q17" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="R17" s="102"/>
+      <c r="S17" s="104"/>
+      <c r="T17" s="102"/>
+      <c r="U17" s="104"/>
+      <c r="V17" s="105"/>
+      <c r="W17" s="105"/>
+      <c r="X17" s="99"/>
+      <c r="Y17" s="99"/>
+      <c r="Z17" s="99"/>
+      <c r="AA17" s="99"/>
+      <c r="AB17" s="99"/>
+      <c r="AC17" s="102"/>
+      <c r="AD17" s="99"/>
+      <c r="AE17" s="99"/>
+      <c r="AF17" s="99"/>
+    </row>
+    <row r="18" spans="1:32" s="84" customFormat="1" ht="152.25">
+      <c r="A18" s="126" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="127" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="128">
+        <v>26000</v>
+      </c>
+      <c r="E18" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="126">
+        <v>0</v>
+      </c>
+      <c r="H18" s="126">
+        <v>200</v>
+      </c>
+      <c r="I18" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="J18" s="129" t="s">
+        <v>118</v>
+      </c>
+      <c r="K18" s="130">
+        <f>(27+15)/67</f>
+        <v>0.62686567164179108</v>
+      </c>
+      <c r="L18" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="M18" s="71" t="s">
+        <v>90</v>
+      </c>
+      <c r="N18" s="79" t="s">
+        <v>64</v>
+      </c>
+      <c r="O18" s="71" t="s">
+        <v>56</v>
+      </c>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="71"/>
+      <c r="S18" s="80"/>
+      <c r="T18" s="71"/>
+      <c r="U18" s="80"/>
+      <c r="X18" s="129"/>
+      <c r="Y18" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z18" s="129"/>
+      <c r="AA18" s="131" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB18" s="131" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC18" s="71"/>
+      <c r="AD18" s="131"/>
+      <c r="AE18" s="131"/>
+      <c r="AF18" s="131"/>
+    </row>
+    <row r="25" spans="1:32">
+      <c r="C25" s="132"/>
+    </row>
+    <row r="26" spans="1:32">
+      <c r="C26" s="132"/>
+    </row>
+    <row r="27" spans="1:32">
+      <c r="C27" s="132"/>
+    </row>
+    <row r="28" spans="1:32">
+      <c r="C28" s="132"/>
+    </row>
+    <row r="29" spans="1:32">
+      <c r="C29" s="132"/>
+    </row>
+    <row r="30" spans="1:32">
+      <c r="C30" s="132"/>
+    </row>
+    <row r="31" spans="1:32">
+      <c r="C31" s="132"/>
+    </row>
+  </sheetData>
+  <dataValidations count="13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P19:Q20 AB2:AB18" xr:uid="{AEC86146-C095-4E09-B1B0-13459C32A4C0}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P18 AD2:AD18" xr:uid="{B9803342-1FF2-4DA6-9372-1D76BD207C06}">
+      <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O19:O20 N2:N18 AA2:AA18" xr:uid="{8B2C8F2E-AE12-4684-8F76-2CB6106B85BF}">
+      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S19:S29 Q2:Q18 AE2:AE18" xr:uid="{508038E3-60F3-48F1-A83F-7166C2F1592F}">
+      <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T19:T32 AF2:AF18" xr:uid="{3C7D347C-284B-4766-B258-7D87F1E945A7}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O18" xr:uid="{FBCF090D-AA1E-4D00-9B80-8D91060492A6}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M18" xr:uid="{46328FA5-EE5D-4C04-BD25-FE8EB21A87F8}">
+      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T18" xr:uid="{3A76D258-0A26-45F2-A3F3-715A1D507E12}">
+      <formula1>"National, Regional, City, Community"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L18" xr:uid="{1CEC30F7-4943-455D-ACAB-6887E8EBA589}">
+      <formula1>"Non-VF, VF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R18" xr:uid="{01BB03C9-3946-406B-BA09-3E427F069545}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S18" xr:uid="{9A24D61D-8532-4025-BB2E-8E5C939FD3B9}">
+      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC13 AB14 AC15:AC18" xr:uid="{877DD6BF-3291-4236-B017-CA736978590E}">
+      <formula1>"Tier 1, Tier 2, Tier 3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E5 E7:E16" xr:uid="{33F76EFD-AD55-4B69-978A-D8A8ECD8EE3E}">
+      <formula1>$A$2:$A$22</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{ECBF53F7-5E7A-4FEE-A95A-7B3E3A5720AC}"/>
+    <hyperlink ref="C9" r:id="rId2" xr:uid="{EE72C64C-3166-4964-9C25-24A6429EE0AE}"/>
+    <hyperlink ref="C18" r:id="rId3" xr:uid="{CBFA03A0-AD72-4692-966C-69BEF40C361E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="2" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="72" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="99" t="s">
+    <row r="2" spans="1:2" ht="43.5">
+      <c r="A2" s="149" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="74" t="s">
-        <v>84</v>
+      <c r="B2" s="73" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="99" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="74" t="s">
+      <c r="A3" s="149" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="73" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="29.1">
+      <c r="A4" s="149" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="73" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="29.1">
+      <c r="A5" s="149" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="73" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="87">
+      <c r="A6" s="149" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="73" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="43.5">
+      <c r="A7" s="149" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="73" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="43.5">
+      <c r="A8" s="149" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="73" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="43.5">
+      <c r="A9" s="149" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="29.1">
+      <c r="A10" s="149" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="150" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="29.1">
+      <c r="A11" s="149" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="150" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="43.5">
+      <c r="A12" s="149" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="73" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="29.1">
+      <c r="A13" s="149" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="150" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="149" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="150" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="29.1">
+      <c r="A15" s="149" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="150" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="29.1">
+      <c r="A16" s="149" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" s="150" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="29.1">
+      <c r="A17" s="149" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="73" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29.1">
+      <c r="A18" s="149" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="150" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="72.599999999999994">
+      <c r="A19" s="149" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="150" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="29.1">
+      <c r="A20" s="149" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="99" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="74" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="99" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="74" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="99" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" s="74" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="99" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="74" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="99" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" s="74" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="99" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="74" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="99" t="s">
-        <v>98</v>
-      </c>
-      <c r="B10" s="100" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="99" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="100" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="99" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="74" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="99" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="100" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="99" t="s">
-        <v>104</v>
-      </c>
-      <c r="B14" s="100" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="100" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="99" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" s="100" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="99" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="74" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="99" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="100" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="99" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="100" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="99" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="100" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="99" t="s">
+      <c r="B20" s="150" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="43.5">
+      <c r="A21" s="149" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="101" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="99" t="s">
-        <v>116</v>
-      </c>
-      <c r="B22" s="100" t="s">
-        <v>117</v>
+      <c r="B21" s="151" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="29.1">
+      <c r="A22" s="149" t="s">
+        <v>151</v>
+      </c>
+      <c r="B22" s="150" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/01_Input/00_CO Validation/Trinidad & Tobago - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Trinidad & Tobago - Energy Projects.xlsx
@@ -320,7 +320,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -779,9 +779,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -881,6 +878,26 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K19" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L19" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4424,9 +4441,8 @@
           <t xml:space="preserve">GEF SGP </t>
         </is>
       </c>
-      <c r="O18" s="130">
-        <f>(27+15)/67</f>
-        <v/>
+      <c r="O18" s="130" t="n">
+        <v>0.6268656716417911</v>
       </c>
       <c r="P18" s="133" t="inlineStr">
         <is>
@@ -4490,37 +4506,33 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K19" s="126" t="n">
+      <c r="K19" s="158" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="158" t="n"/>
-      <c r="M19" s="159" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
-      <c r="N19" s="160" t="n"/>
-      <c r="O19" s="161" t="n"/>
-      <c r="P19" s="162" t="n"/>
+      <c r="M19" s="52" t="n"/>
+      <c r="N19" s="159" t="n"/>
+      <c r="O19" s="160" t="n"/>
+      <c r="P19" s="161" t="n"/>
       <c r="Q19" s="157" t="n"/>
-      <c r="R19" s="162" t="n"/>
-      <c r="S19" s="162" t="n"/>
-      <c r="T19" s="162" t="n"/>
-      <c r="U19" s="162" t="n"/>
-      <c r="V19" s="163" t="n"/>
-      <c r="W19" s="162" t="n"/>
-      <c r="X19" s="163" t="n"/>
-      <c r="Y19" s="164" t="n"/>
-      <c r="Z19" s="164" t="n"/>
-      <c r="AA19" s="160" t="n"/>
+      <c r="R19" s="161" t="n"/>
+      <c r="S19" s="161" t="n"/>
+      <c r="T19" s="161" t="n"/>
+      <c r="U19" s="161" t="n"/>
+      <c r="V19" s="162" t="n"/>
+      <c r="W19" s="161" t="n"/>
+      <c r="X19" s="162" t="n"/>
+      <c r="Y19" s="163" t="n"/>
+      <c r="Z19" s="163" t="n"/>
+      <c r="AA19" s="159" t="n"/>
       <c r="AB19" s="30" t="n"/>
-      <c r="AC19" s="160" t="n"/>
-      <c r="AD19" s="165" t="n"/>
-      <c r="AE19" s="165" t="n"/>
-      <c r="AF19" s="162" t="n"/>
-      <c r="AG19" s="165" t="n"/>
-      <c r="AH19" s="165" t="n"/>
-      <c r="AI19" s="165" t="n"/>
+      <c r="AC19" s="159" t="n"/>
+      <c r="AD19" s="164" t="n"/>
+      <c r="AE19" s="164" t="n"/>
+      <c r="AF19" s="161" t="n"/>
+      <c r="AG19" s="164" t="n"/>
+      <c r="AH19" s="164" t="n"/>
+      <c r="AI19" s="164" t="n"/>
     </row>
     <row r="20"/>
     <row r="21"/>
@@ -4550,7 +4562,7 @@
       <c r="C32" s="132" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="16">
+  <dataValidations count="14">
     <dataValidation sqref="P19:Q20 AB2:AB18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
@@ -4593,12 +4605,6 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
@@ -4606,6 +4612,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -4623,288 +4630,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="166" t="inlineStr">
+      <c r="A1" s="165" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="166" t="inlineStr">
+      <c r="B1" s="165" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="43.5" customHeight="1">
-      <c r="A2" s="167" t="inlineStr">
+      <c r="A2" s="166" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="167" t="inlineStr">
+      <c r="B2" s="166" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="167" t="inlineStr">
+      <c r="A3" s="166" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="167" t="inlineStr">
+      <c r="B3" s="166" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="29.1" customHeight="1">
-      <c r="A4" s="167" t="inlineStr">
+      <c r="A4" s="166" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="167" t="inlineStr">
+      <c r="B4" s="166" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="29.1" customHeight="1">
-      <c r="A5" s="167" t="inlineStr">
+      <c r="A5" s="166" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="167" t="inlineStr">
+      <c r="B5" s="166" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="87" customHeight="1">
-      <c r="A6" s="167" t="inlineStr">
+      <c r="A6" s="166" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="167" t="inlineStr">
+      <c r="B6" s="166" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="43.5" customHeight="1">
-      <c r="A7" s="167" t="inlineStr">
+      <c r="A7" s="166" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="167" t="inlineStr">
+      <c r="B7" s="166" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="43.5" customHeight="1">
-      <c r="A8" s="167" t="inlineStr">
+      <c r="A8" s="166" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="167" t="inlineStr">
+      <c r="B8" s="166" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="43.5" customHeight="1">
-      <c r="A9" s="167" t="inlineStr">
+      <c r="A9" s="166" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="167" t="inlineStr">
+      <c r="B9" s="166" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="29.1" customHeight="1">
-      <c r="A10" s="167" t="inlineStr">
+      <c r="A10" s="166" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="167" t="inlineStr">
+      <c r="B10" s="166" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="29.1" customHeight="1">
-      <c r="A11" s="167" t="inlineStr">
+      <c r="A11" s="166" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="167" t="inlineStr">
+      <c r="B11" s="166" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="43.5" customHeight="1">
-      <c r="A12" s="167" t="inlineStr">
+      <c r="A12" s="166" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="167" t="inlineStr">
+      <c r="B12" s="166" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="29.1" customHeight="1">
-      <c r="A13" s="167" t="inlineStr">
+      <c r="A13" s="166" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="167" t="inlineStr">
+      <c r="B13" s="166" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="167" t="inlineStr">
+      <c r="A14" s="166" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="167" t="inlineStr">
+      <c r="B14" s="166" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="29.1" customHeight="1">
-      <c r="A15" s="167" t="inlineStr">
+      <c r="A15" s="166" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="167" t="inlineStr">
+      <c r="B15" s="166" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="29.1" customHeight="1">
-      <c r="A16" s="167" t="inlineStr">
+      <c r="A16" s="166" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="167" t="inlineStr">
+      <c r="B16" s="166" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="29.1" customHeight="1">
-      <c r="A17" s="167" t="inlineStr">
+      <c r="A17" s="166" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="167" t="inlineStr">
+      <c r="B17" s="166" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="29.1" customHeight="1">
-      <c r="A18" s="167" t="inlineStr">
+      <c r="A18" s="166" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="167" t="inlineStr">
+      <c r="B18" s="166" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="72.59999999999999" customHeight="1">
-      <c r="A19" s="167" t="inlineStr">
+      <c r="A19" s="166" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="167" t="inlineStr">
+      <c r="B19" s="166" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="29.1" customHeight="1">
-      <c r="A20" s="167" t="inlineStr">
+      <c r="A20" s="166" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="167" t="inlineStr">
+      <c r="B20" s="166" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="43.5" customHeight="1">
-      <c r="A21" s="167" t="inlineStr">
+      <c r="A21" s="166" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="167" t="inlineStr">
+      <c r="B21" s="166" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="29.1" customHeight="1">
-      <c r="A22" s="167" t="inlineStr">
+      <c r="A22" s="166" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="167" t="inlineStr">
+      <c r="B22" s="166" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="167" t="inlineStr">
+      <c r="A23" s="166" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="167" t="inlineStr">
+      <c r="B23" s="166" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="167" t="inlineStr">
+      <c r="A24" s="166" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="167" t="inlineStr">
+      <c r="B24" s="166" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
